--- a/data/source/Ganeinu_Assessments_for_Kriah_Curriculum.xlsx
+++ b/data/source/Ganeinu_Assessments_for_Kriah_Curriculum.xlsx
@@ -435,7 +435,7 @@
       </c>
       <c r="H2" t="str" xml:space="preserve">
         <v xml:space="preserve">Sheva in _x000d_
-Begining </v>
+Beginning </v>
       </c>
       <c r="I2" t="str" xml:space="preserve">
         <v xml:space="preserve">Sheva in _x000d_
@@ -471,7 +471,7 @@
       </c>
       <c r="Q2" t="str" xml:space="preserve">
         <v xml:space="preserve">Shuruk in _x000d_
-begining</v>
+beginning</v>
       </c>
       <c r="R2" t="str" xml:space="preserve">
         <v xml:space="preserve">Confusing Dagesh_x000d_
